--- a/01.server_setup/03.ip_address_management/IPAM.xlsx
+++ b/01.server_setup/03.ip_address_management/IPAM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Git_Projects\Network-Automation-Lab\01.server_setup\03.ip_address_management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92ADA110-9DD1-4911-900F-46BF3031A15D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD29EAD9-D19A-4A3C-A08A-5C7C77B20DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8C872FB1-40B1-4F13-9BAC-9C3F2D991F53}"/>
   </bookViews>
@@ -723,6 +723,18 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -748,18 +760,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1123,10 +1123,10 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="16">
+      <c r="B3" s="20">
         <v>1</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
@@ -1140,8 +1140,8 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="17"/>
-      <c r="C4" s="14"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="18"/>
       <c r="D4" s="3" t="s">
         <v>5</v>
       </c>
@@ -1153,12 +1153,12 @@
       </c>
     </row>
     <row r="5" spans="2:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="18"/>
-      <c r="C5" s="15"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="19"/>
       <c r="D5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="25" t="s">
+      <c r="E5" s="16" t="s">
         <v>123</v>
       </c>
       <c r="F5" s="8" t="s">
@@ -1166,10 +1166,10 @@
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B6" s="16">
+      <c r="B6" s="20">
         <v>2</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="17" t="s">
         <v>4</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -1183,8 +1183,8 @@
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="14"/>
+      <c r="B7" s="21"/>
+      <c r="C7" s="18"/>
       <c r="D7" s="3" t="s">
         <v>5</v>
       </c>
@@ -1196,8 +1196,8 @@
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B8" s="18"/>
-      <c r="C8" s="15"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="19"/>
       <c r="D8" s="3" t="s">
         <v>33</v>
       </c>
@@ -1209,10 +1209,10 @@
       </c>
     </row>
     <row r="9" spans="2:6" ht="68.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="16">
+      <c r="B9" s="20">
         <v>3</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="17" t="s">
         <v>6</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -1226,8 +1226,8 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B10" s="17"/>
-      <c r="C10" s="14"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="18"/>
       <c r="D10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1239,8 +1239,8 @@
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B11" s="17"/>
-      <c r="C11" s="14"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="18"/>
       <c r="D11" s="3" t="s">
         <v>5</v>
       </c>
@@ -1252,8 +1252,8 @@
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B12" s="17"/>
-      <c r="C12" s="14"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="18"/>
       <c r="D12" s="3" t="s">
         <v>9</v>
       </c>
@@ -1265,8 +1265,8 @@
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B13" s="18"/>
-      <c r="C13" s="15"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="19"/>
       <c r="D13" s="3" t="s">
         <v>33</v>
       </c>
@@ -1278,10 +1278,10 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B14" s="19">
+      <c r="B14" s="23">
         <v>4</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" s="17" t="s">
         <v>8</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -1295,8 +1295,8 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B15" s="20"/>
-      <c r="C15" s="14"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="18"/>
       <c r="D15" s="3" t="s">
         <v>7</v>
       </c>
@@ -1308,8 +1308,8 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B16" s="20"/>
-      <c r="C16" s="14"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="3" t="s">
         <v>3</v>
       </c>
@@ -1321,8 +1321,8 @@
       </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="20"/>
-      <c r="C17" s="14"/>
+      <c r="B17" s="24"/>
+      <c r="C17" s="18"/>
       <c r="D17" s="3" t="s">
         <v>11</v>
       </c>
@@ -1334,8 +1334,8 @@
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="20"/>
-      <c r="C18" s="14"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="18"/>
       <c r="D18" s="3" t="s">
         <v>52</v>
       </c>
@@ -1347,12 +1347,12 @@
       </c>
     </row>
     <row r="19" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B19" s="21"/>
-      <c r="C19" s="15"/>
+      <c r="B19" s="25"/>
+      <c r="C19" s="19"/>
       <c r="D19" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="25" t="s">
+      <c r="E19" s="16" t="s">
         <v>126</v>
       </c>
       <c r="F19" s="8" t="s">
@@ -1360,10 +1360,10 @@
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="16">
+      <c r="B20" s="20">
         <v>5</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="17" t="s">
         <v>10</v>
       </c>
       <c r="D20" s="3" t="s">
@@ -1377,8 +1377,8 @@
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="17"/>
-      <c r="C21" s="14"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="3" t="s">
         <v>7</v>
       </c>
@@ -1390,8 +1390,8 @@
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="17"/>
-      <c r="C22" s="14"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1403,8 +1403,8 @@
       </c>
     </row>
     <row r="23" spans="2:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="B23" s="17"/>
-      <c r="C23" s="14"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="18"/>
       <c r="D23" s="3" t="s">
         <v>64</v>
       </c>
@@ -1416,8 +1416,8 @@
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="18"/>
-      <c r="C24" s="15"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="19"/>
       <c r="D24" s="3" t="s">
         <v>33</v>
       </c>
@@ -1429,10 +1429,10 @@
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="16">
+      <c r="B25" s="20">
         <v>6</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="17" t="s">
         <v>68</v>
       </c>
       <c r="D25" s="3" t="s">
@@ -1446,8 +1446,8 @@
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="17"/>
-      <c r="C26" s="14"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="18"/>
       <c r="D26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1459,8 +1459,8 @@
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="17"/>
-      <c r="C27" s="14"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="18"/>
       <c r="D27" s="3" t="s">
         <v>5</v>
       </c>
@@ -1472,8 +1472,8 @@
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="18"/>
-      <c r="C28" s="15"/>
+      <c r="B28" s="22"/>
+      <c r="C28" s="19"/>
       <c r="D28" s="3" t="s">
         <v>33</v>
       </c>
@@ -1485,10 +1485,10 @@
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="16">
+      <c r="B29" s="20">
         <v>7</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" s="17" t="s">
         <v>12</v>
       </c>
       <c r="D29" s="3" t="s">
@@ -1502,8 +1502,8 @@
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="17"/>
-      <c r="C30" s="14"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="18"/>
       <c r="D30" s="3" t="s">
         <v>7</v>
       </c>
@@ -1515,8 +1515,8 @@
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="17"/>
-      <c r="C31" s="14"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="18"/>
       <c r="D31" s="3" t="s">
         <v>3</v>
       </c>
@@ -1528,8 +1528,8 @@
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="17"/>
-      <c r="C32" s="14"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="18"/>
       <c r="D32" s="3" t="s">
         <v>9</v>
       </c>
@@ -1541,8 +1541,8 @@
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="18"/>
-      <c r="C33" s="15"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="19"/>
       <c r="D33" s="3" t="s">
         <v>33</v>
       </c>
@@ -1554,10 +1554,10 @@
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="16">
+      <c r="B34" s="20">
         <v>8</v>
       </c>
-      <c r="C34" s="13" t="s">
+      <c r="C34" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D34" s="3" t="s">
@@ -1571,8 +1571,8 @@
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="17"/>
-      <c r="C35" s="14"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="18"/>
       <c r="D35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,8 +1584,8 @@
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="18"/>
-      <c r="C36" s="15"/>
+      <c r="B36" s="22"/>
+      <c r="C36" s="19"/>
       <c r="D36" s="3" t="s">
         <v>33</v>
       </c>
@@ -1597,10 +1597,10 @@
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="16">
+      <c r="B37" s="20">
         <v>9</v>
       </c>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="13" t="s">
         <v>14</v>
       </c>
       <c r="D37" s="3" t="s">
@@ -1614,8 +1614,8 @@
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="17"/>
-      <c r="C38" s="23"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="14"/>
       <c r="D38" s="3" t="s">
         <v>91</v>
       </c>
@@ -1627,8 +1627,8 @@
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="18"/>
-      <c r="C39" s="24"/>
+      <c r="B39" s="22"/>
+      <c r="C39" s="15"/>
       <c r="D39" s="3" t="s">
         <v>33</v>
       </c>
@@ -1640,10 +1640,10 @@
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="16">
+      <c r="B40" s="20">
         <v>10</v>
       </c>
-      <c r="C40" s="13" t="s">
+      <c r="C40" s="17" t="s">
         <v>15</v>
       </c>
       <c r="D40" s="3" t="s">
@@ -1657,8 +1657,8 @@
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B41" s="17"/>
-      <c r="C41" s="14"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="18"/>
       <c r="D41" s="3" t="s">
         <v>97</v>
       </c>
@@ -1670,8 +1670,8 @@
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="18"/>
-      <c r="C42" s="15"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="19"/>
       <c r="D42" s="3" t="s">
         <v>33</v>
       </c>
@@ -1683,10 +1683,10 @@
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B43" s="16">
+      <c r="B43" s="20">
         <v>11</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="17" t="s">
         <v>16</v>
       </c>
       <c r="D43" s="3" t="s">
@@ -1700,10 +1700,10 @@
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B44" s="17">
+      <c r="B44" s="21">
         <v>11</v>
       </c>
-      <c r="C44" s="14"/>
+      <c r="C44" s="18"/>
       <c r="D44" s="3" t="s">
         <v>102</v>
       </c>
@@ -1715,10 +1715,10 @@
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B45" s="18">
+      <c r="B45" s="22">
         <v>11</v>
       </c>
-      <c r="C45" s="15"/>
+      <c r="C45" s="19"/>
       <c r="D45" s="3" t="s">
         <v>33</v>
       </c>
@@ -1730,10 +1730,10 @@
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="16">
+      <c r="B46" s="20">
         <v>12</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="17" t="s">
         <v>17</v>
       </c>
       <c r="D46" s="3" t="s">
@@ -1747,10 +1747,10 @@
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="17">
+      <c r="B47" s="21">
         <v>12</v>
       </c>
-      <c r="C47" s="14"/>
+      <c r="C47" s="18"/>
       <c r="D47" s="3" t="s">
         <v>102</v>
       </c>
@@ -1762,10 +1762,10 @@
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="18">
+      <c r="B48" s="22">
         <v>12</v>
       </c>
-      <c r="C48" s="15"/>
+      <c r="C48" s="19"/>
       <c r="D48" s="3" t="s">
         <v>33</v>
       </c>
@@ -1777,10 +1777,10 @@
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B49" s="16">
+      <c r="B49" s="20">
         <v>13</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="17" t="s">
         <v>18</v>
       </c>
       <c r="D49" s="3" t="s">
@@ -1794,8 +1794,8 @@
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B50" s="17"/>
-      <c r="C50" s="14"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="18"/>
       <c r="D50" s="3" t="s">
         <v>102</v>
       </c>
@@ -1807,8 +1807,8 @@
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B51" s="18"/>
-      <c r="C51" s="15"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="19"/>
       <c r="D51" s="3" t="s">
         <v>33</v>
       </c>
@@ -1820,10 +1820,10 @@
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B52" s="16">
+      <c r="B52" s="20">
         <v>14</v>
       </c>
-      <c r="C52" s="13" t="s">
+      <c r="C52" s="17" t="s">
         <v>19</v>
       </c>
       <c r="D52" s="3" t="s">
@@ -1837,10 +1837,10 @@
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B53" s="17">
+      <c r="B53" s="21">
         <v>14</v>
       </c>
-      <c r="C53" s="14"/>
+      <c r="C53" s="18"/>
       <c r="D53" s="3" t="s">
         <v>3</v>
       </c>
@@ -1852,10 +1852,10 @@
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B54" s="18">
+      <c r="B54" s="22">
         <v>14</v>
       </c>
-      <c r="C54" s="15"/>
+      <c r="C54" s="19"/>
       <c r="D54" s="3" t="s">
         <v>33</v>
       </c>
@@ -1885,6 +1885,23 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C9:C13"/>
+    <mergeCell ref="B9:B13"/>
+    <mergeCell ref="C14:C19"/>
+    <mergeCell ref="B14:B19"/>
+    <mergeCell ref="C20:C24"/>
+    <mergeCell ref="B20:B24"/>
+    <mergeCell ref="C25:C28"/>
+    <mergeCell ref="B25:B28"/>
+    <mergeCell ref="C29:C33"/>
+    <mergeCell ref="B29:B33"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B39"/>
     <mergeCell ref="C49:C51"/>
     <mergeCell ref="B49:B51"/>
     <mergeCell ref="C52:C54"/>
@@ -1895,23 +1912,6 @@
     <mergeCell ref="B43:B45"/>
     <mergeCell ref="C46:C48"/>
     <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C29:C33"/>
-    <mergeCell ref="B29:B33"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C14:C19"/>
-    <mergeCell ref="B14:B19"/>
-    <mergeCell ref="C20:C24"/>
-    <mergeCell ref="B20:B24"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="B25:B28"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C9:C13"/>
-    <mergeCell ref="B9:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
